--- a/tools/_out/groupD_20261021/stage/DesignTable_6701T.xlsx
+++ b/tools/_out/groupD_20261021/stage/DesignTable_6701T.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>OMi 6701T bent-tube review table (gen_bent.py) | group D stage 2026-10-21 | 7 OMi rows, 4 ASSUMED | Brennan CAD records decoded on the family STEPs + Air-Way s115 first | NOT SHIPPED</t>
+          <t>OMi 6701T bent-tube review table (gen_bent.py) | group D stage 2026-10-21 | 7 OMi rows, 5 ASSUMED | Brennan CAD records decoded on the family STEPs + Air-Way s115 first | NOT SHIPPED</t>
         </is>
       </c>
     </row>
@@ -471,40 +471,45 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>NECKD@SWSK</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>$PRP@TubeOD</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>$PRP@PartNo</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>$PRP@DataStatus</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>$PRP@AxialSource</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>$COMMENT</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>$PRP@ScopeAction</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>$PRP@DimSource</t>
         </is>
@@ -543,42 +548,45 @@
       <c r="J3" t="n">
         <v>0.354</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>6701-04-04</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-04-04 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Brennan record 6701-04-04: M 1.25 L 1.09 F 0.194 J 0.125 LN 0.649 C1 0.5 C2 0.563 THK 0.197 DIA 0.315 DIA6 0.167 R 0.354. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record.</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>Brennan record 6701-04-04: M 1.25 L 1.09 F 0.194 J 0.125 LN 0.649 C1 0.5 C2 0.563 THK 0.197 DIA 0.315 DIA6 0.167 R 0.354. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record. Swivel neck 0.374 from the part's own STEP (BRENNAN_6701-04-04.stp: body cylinder 0.374 from the nut back (y 0.771) to the tube end (y 0.896 / 0.901) = record DIA4; SWIV_MEAS -04 neck 0.293 &lt; the 0.315 tube).</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>6701-04-04</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>BRENNAN</t>
         </is>
@@ -617,42 +625,45 @@
       <c r="J4" t="n">
         <v>0.512</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.375</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>6701-06-06</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-06-06 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Brennan record 6701-06-06: M 1.35 L 1.22 F 0.234 J 0.14 LN 0.735 C1 0.625 C2 0.688 THK 0.197 DIA 0.413 DIA6 0.256 R 0.512. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record.</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>Brennan record 6701-06-06: M 1.35 L 1.22 F 0.234 J 0.14 LN 0.735 C1 0.625 C2 0.688 THK 0.197 DIA 0.413 DIA6 0.256 R 0.512. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record. Swivel neck 0.494 from the part's own STEP (BRENNAN_6701-06-06.stp: body cylinder 0.494 from the nut back (y 0.846) to the tube end (y 0.986 / 0.995) = record DIA4; SWIV_MEAS -06 neck 0.412 &lt; the 0.413 tube).</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>6701-06-06</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>BRENNAN</t>
         </is>
@@ -691,42 +702,42 @@
       <c r="J5" t="n">
         <v>0.827</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>6701-08-08</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-08-08 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Brennan record 6701-08-08: M 1.77 L 1.52 F 0.264 J 0.155 LN 0.827 C1 0.812 C2 0.875 THK 0.197 DIA 0.549 DIA6 0.374 R 0.827. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>6701-08-08</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>BRENNAN</t>
         </is>
@@ -765,42 +776,42 @@
       <c r="J6" t="n">
         <v>1.181</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>6701-12-12</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-12-12 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Brennan record 6701-12-12: M 2.5 L 2.4 F 0.314 J 0.185 LN 1.047 C1 1.125 C2 1.25 THK 0.276 DIA 0.799 DIA6 0.591 R 1.181. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record.</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>6701-12-12</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>BRENNAN</t>
         </is>
@@ -821,42 +832,42 @@
       <c r="F7" t="n">
         <v>1.5</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>6701-16-16</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>[BRENNAN-CATALOG 2026-10-21: M1 CHEX NUTHEX] Brennan TFA catalog TFA-p038-t02 6701-16-16 | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>catalog 6701-16-16: M 3.10 L 3.15 C1 1.375 C2 1.500. HELD: no Brennan CAD record (PARTcommunity: none) and no -16 6701 STEP: tube OD / bore / bend radius / hex length / nut position have no source (catalog p38 gives only M 3.10 / L 3.15 / C1 1.375 / C2 1.500) - needs BRENNAN_6701-16-16.stp</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>catalog 6701-16-16: M 3.10 L 3.15 C1 1.375 C2 1.500. HELD: no Brennan CAD record (PARTcommunity: none) and no STEP (user 2026-10-21: nothing available): tube OD / bore / bend radius / hex length / nut position have no source (catalog p38 gives only M 3.10 / L 3.15 / C1 1.375 / C2 1.500)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>6701-16-16</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>BRENNAN</t>
         </is>
@@ -868,6 +879,9 @@
           <t>6701-20-20</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>3.26</v>
+      </c>
       <c r="C8" t="n">
         <v>4.335</v>
       </c>
@@ -892,42 +906,42 @@
       <c r="J8" t="n">
         <v>1.89</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>6701-20-20</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-20-20 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Brennan record 6701-20-20: M 3.26 L 3.75 F 0.37 J 0.19 LN 1.145 C1 1.693 C2 2.0 THK 0.315 DIA 1.26 DIA6 1.024 R 1.89. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record. HELD: M conflict between two Brennan sources: CAD record M 3.260 vs TFA catalog p38 M 2.750 (L 3.750 in both; the -16 has M 3.10) - never picked silently; Q-GD-6701-20 (the record value 3.26 fits the size series)</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>Brennan record 6701-20-20: M 3.26 L 3.75 F 0.37 J 0.19 LN 1.145 C1 1.693 C2 2.0 THK 0.315 DIA 1.26 DIA6 1.024 R 1.89. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record. BRENNAN_6701-20-20.stp: JIC tip x -3.260 = M 3.26 (CAD record); the TFA catalog p38 M 2.750 is a misprint; nut face y 4.335 = L - F - J + LN; torus R 1.890, tube 1.260 / 1.024.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>6701-20-20</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>BRENNAN</t>
         </is>
@@ -948,42 +962,42 @@
       <c r="F9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>6701-L-16-16</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>[BRENNAN-CATALOG 2026-10-21: M1 CHEX NUTHEX] Brennan TFA catalog TFA-p038-t03 6701-L-16-16 | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>catalog 6701-L-16-16: M 3.125 L 4.870 C1 1.375 C2 1.500. HELD: no Brennan CAD record (PARTcommunity: none) and no 6701-L STEP: tube OD / bore / bend radius / hex length / nut position have no source (catalog p38 6701-L gives only L 4.870 / M 3.125 / C1 1.375 / C2 1.500) - needs BRENNAN_6701-L-16-16.stp</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>catalog 6701-L-16-16: M 3.125 L 4.870 C1 1.375 C2 1.500. HELD: no Brennan CAD record (PARTcommunity: none) and no STEP (user 2026-10-21: nothing available): tube OD / bore / bend radius / hex length / nut position have no source (catalog p38 6701-L gives only L 4.870 / M 3.125 / C1 1.375 / C2 1.500)</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>6701-L-16-16</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>BRENNAN</t>
         </is>
